--- a/artfynd/A 44193-2023 artfynd.xlsx
+++ b/artfynd/A 44193-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121374053</v>
+        <v>121374098</v>
       </c>
       <c r="B2" t="n">
-        <v>56560</v>
+        <v>56563</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>honfärgad</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -735,14 +735,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nordanstig, Klövbergets NR, Attmar, Mpd</t>
+          <t>Nordanstig, Mokojan  Attmar, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584855</v>
+        <v>584807</v>
       </c>
       <c r="R2" t="n">
-        <v>6900129</v>
+        <v>6900247</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,11 +777,6 @@
           <t>2024-08-18</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1 höna 4  kycklingar</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -802,18 +797,14 @@
           <t>Hans Forsberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Skogsfågelinventering i Västernorrland</t>
-        </is>
-      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121374098</v>
+        <v>121374112</v>
       </c>
       <c r="B3" t="n">
-        <v>56560</v>
+        <v>56563</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -855,7 +846,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -874,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584807</v>
+        <v>584985</v>
       </c>
       <c r="R3" t="n">
-        <v>6900247</v>
+        <v>6900177</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -932,14 +923,18 @@
           <t>Hans Forsberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skogsfågelinventering i Västernorrland</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121374112</v>
+        <v>121374053</v>
       </c>
       <c r="B4" t="n">
-        <v>56560</v>
+        <v>56563</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -971,7 +966,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -981,7 +976,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>honfärgad</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -996,14 +991,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nordanstig, Mokojan  Attmar, Mpd</t>
+          <t>Nordanstig, Klövbergets NR, Attmar, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584985</v>
+        <v>584855</v>
       </c>
       <c r="R4" t="n">
-        <v>6900177</v>
+        <v>6900129</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1036,6 +1031,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 höna 4  kycklingar</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 44193-2023 artfynd.xlsx
+++ b/artfynd/A 44193-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121374098</v>
+        <v>121374053</v>
       </c>
       <c r="B2" t="n">
         <v>56563</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>honfärgad</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -735,14 +735,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nordanstig, Mokojan  Attmar, Mpd</t>
+          <t>Nordanstig, Klövbergets NR, Attmar, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584807</v>
+        <v>584855</v>
       </c>
       <c r="R2" t="n">
-        <v>6900247</v>
+        <v>6900129</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,6 +777,11 @@
           <t>2024-08-18</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1 höna 4  kycklingar</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -797,11 +802,15 @@
           <t>Hans Forsberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skogsfågelinventering i Västernorrland</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121374112</v>
+        <v>121374098</v>
       </c>
       <c r="B3" t="n">
         <v>56563</v>
@@ -846,7 +855,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -865,10 +874,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584985</v>
+        <v>584807</v>
       </c>
       <c r="R3" t="n">
-        <v>6900177</v>
+        <v>6900247</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -923,15 +932,11 @@
           <t>Hans Forsberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Skogsfågelinventering i Västernorrland</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121374053</v>
+        <v>121374112</v>
       </c>
       <c r="B4" t="n">
         <v>56563</v>
@@ -966,7 +971,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -976,7 +981,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>honfärgad</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -991,14 +996,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nordanstig, Klövbergets NR, Attmar, Mpd</t>
+          <t>Nordanstig, Mokojan  Attmar, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584855</v>
+        <v>584985</v>
       </c>
       <c r="R4" t="n">
-        <v>6900129</v>
+        <v>6900177</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1031,11 +1036,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1 höna 4  kycklingar</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 44193-2023 artfynd.xlsx
+++ b/artfynd/A 44193-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121374053</v>
+        <v>121374098</v>
       </c>
       <c r="B2" t="n">
-        <v>56563</v>
+        <v>56566</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>honfärgad</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -735,14 +735,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nordanstig, Klövbergets NR, Attmar, Mpd</t>
+          <t>Nordanstig, Mokojan  Attmar, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584855</v>
+        <v>584807</v>
       </c>
       <c r="R2" t="n">
-        <v>6900129</v>
+        <v>6900247</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,11 +777,6 @@
           <t>2024-08-18</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1 höna 4  kycklingar</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -802,18 +797,14 @@
           <t>Hans Forsberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Skogsfågelinventering i Västernorrland</t>
-        </is>
-      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121374098</v>
+        <v>121374112</v>
       </c>
       <c r="B3" t="n">
-        <v>56563</v>
+        <v>56566</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -855,7 +846,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -874,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584807</v>
+        <v>584985</v>
       </c>
       <c r="R3" t="n">
-        <v>6900247</v>
+        <v>6900177</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -932,14 +923,18 @@
           <t>Hans Forsberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skogsfågelinventering i Västernorrland</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121374112</v>
+        <v>121374053</v>
       </c>
       <c r="B4" t="n">
-        <v>56563</v>
+        <v>56566</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -971,7 +966,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -981,7 +976,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>honfärgad</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -996,14 +991,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nordanstig, Mokojan  Attmar, Mpd</t>
+          <t>Nordanstig, Klövbergets NR, Attmar, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584985</v>
+        <v>584855</v>
       </c>
       <c r="R4" t="n">
-        <v>6900177</v>
+        <v>6900129</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1036,6 +1031,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 höna 4  kycklingar</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 44193-2023 artfynd.xlsx
+++ b/artfynd/A 44193-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121374112</v>
+        <v>121374053</v>
       </c>
       <c r="B3" t="n">
         <v>56566</v>
@@ -836,7 +836,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>honfärgad</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -861,14 +861,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nordanstig, Mokojan  Attmar, Mpd</t>
+          <t>Nordanstig, Klövbergets NR, Attmar, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584985</v>
+        <v>584855</v>
       </c>
       <c r="R3" t="n">
-        <v>6900177</v>
+        <v>6900129</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -901,6 +901,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 höna 4  kycklingar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,7 +936,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121374053</v>
+        <v>121374112</v>
       </c>
       <c r="B4" t="n">
         <v>56566</v>
@@ -966,7 +971,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -976,7 +981,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>honfärgad</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -991,14 +996,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nordanstig, Klövbergets NR, Attmar, Mpd</t>
+          <t>Nordanstig, Mokojan  Attmar, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584855</v>
+        <v>584985</v>
       </c>
       <c r="R4" t="n">
-        <v>6900129</v>
+        <v>6900177</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1031,11 +1036,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1 höna 4  kycklingar</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 44193-2023 artfynd.xlsx
+++ b/artfynd/A 44193-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121374098</v>
       </c>
       <c r="B2" t="n">
-        <v>56566</v>
+        <v>56567</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>121374053</v>
       </c>
       <c r="B3" t="n">
-        <v>56566</v>
+        <v>56567</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>121374112</v>
       </c>
       <c r="B4" t="n">
-        <v>56566</v>
+        <v>56567</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 44193-2023 artfynd.xlsx
+++ b/artfynd/A 44193-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121374098</v>
+        <v>121374053</v>
       </c>
       <c r="B2" t="n">
-        <v>56567</v>
+        <v>56568</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>honfärgad</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -735,14 +735,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nordanstig, Mokojan  Attmar, Mpd</t>
+          <t>Nordanstig, Klövbergets NR, Attmar, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584807</v>
+        <v>584855</v>
       </c>
       <c r="R2" t="n">
-        <v>6900247</v>
+        <v>6900129</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,6 +777,11 @@
           <t>2024-08-18</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1 höna 4  kycklingar</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -797,14 +802,18 @@
           <t>Hans Forsberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skogsfågelinventering i Västernorrland</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121374053</v>
+        <v>121374098</v>
       </c>
       <c r="B3" t="n">
-        <v>56567</v>
+        <v>56568</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,7 +845,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -846,7 +855,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>honfärgad</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -861,14 +870,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nordanstig, Klövbergets NR, Attmar, Mpd</t>
+          <t>Nordanstig, Mokojan  Attmar, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584855</v>
+        <v>584807</v>
       </c>
       <c r="R3" t="n">
-        <v>6900129</v>
+        <v>6900247</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -903,11 +912,6 @@
           <t>2024-08-18</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1 höna 4  kycklingar</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -928,18 +932,14 @@
           <t>Hans Forsberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Skogsfågelinventering i Västernorrland</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>121374112</v>
       </c>
       <c r="B4" t="n">
-        <v>56567</v>
+        <v>56568</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 44193-2023 artfynd.xlsx
+++ b/artfynd/A 44193-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121374053</v>
+        <v>121374112</v>
       </c>
       <c r="B2" t="n">
         <v>56568</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>honfärgad</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -735,14 +735,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nordanstig, Klövbergets NR, Attmar, Mpd</t>
+          <t>Nordanstig, Mokojan  Attmar, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584855</v>
+        <v>584985</v>
       </c>
       <c r="R2" t="n">
-        <v>6900129</v>
+        <v>6900177</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -775,11 +775,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1 höna 4  kycklingar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -936,7 +931,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121374112</v>
+        <v>121374053</v>
       </c>
       <c r="B4" t="n">
         <v>56568</v>
@@ -971,7 +966,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -981,7 +976,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>honfärgad</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -996,14 +991,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nordanstig, Mokojan  Attmar, Mpd</t>
+          <t>Nordanstig, Klövbergets NR, Attmar, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584985</v>
+        <v>584855</v>
       </c>
       <c r="R4" t="n">
-        <v>6900177</v>
+        <v>6900129</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1036,6 +1031,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 höna 4  kycklingar</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 44193-2023 artfynd.xlsx
+++ b/artfynd/A 44193-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>121374053</v>
       </c>
       <c r="B2" t="n">
-        <v>56569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,12 +808,7 @@
         <v>121374098</v>
       </c>
       <c r="B3" t="n">
-        <v>56569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -936,15 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121374112</v>
+        <v>121374106</v>
       </c>
       <c r="B4" t="n">
-        <v>56569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,10 +985,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584985</v>
+        <v>584786</v>
       </c>
       <c r="R4" t="n">
-        <v>6900177</v>
+        <v>6900259</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1063,6 +1048,482 @@
           <t>Skogsfågelinventering i Västernorrland</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121374112</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nordanstig, Mokojan  Attmar, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>584985</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6900177</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Hans Forsberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hans Forsberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Skogsfågelinventering i Västernorrland</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113283700</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Klövtjärn, Klövbergets NR, Attmar, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>585128</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6899836</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hans Forsberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hans Forsberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>107174426</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Klövtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>584922</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6900116</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-07-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-07-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hans Forsberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hans Forsberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113283704</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Klövtjärn, Klövbergets NR, Attmar, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>585039</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6900111</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Hans Forsberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Hans Forsberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44193-2023 artfynd.xlsx
+++ b/artfynd/A 44193-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Skogsfågelinventering i Västernorrland</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121374053</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -923,6 +933,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121374098</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1048,6 +1063,11 @@
           <t>Skogsfågelinventering i Västernorrland</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121374106</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1173,6 +1193,11 @@
           <t>Skogsfågelinventering i Västernorrland</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121374112</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1290,6 +1315,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113283700</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1407,6 +1437,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107174426</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1524,8 +1559,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113283704</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>